--- a/google-sheets/GP2T-Planilha-Diretoria-EXEMPLO.xlsx
+++ b/google-sheets/GP2T-Planilha-Diretoria-EXEMPLO.xlsx
@@ -2020,7 +2020,7 @@
       </c>
       <c r="B3" s="30" t="inlineStr">
         <is>
-          <t>Hora</t>
+          <t>Horário</t>
         </is>
       </c>
       <c r="C3" s="30" t="inlineStr">
